--- a/工作记录.xlsx
+++ b/工作记录.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>日期</t>
   </si>
@@ -1275,13 +1275,13 @@
     </r>
   </si>
   <si>
-    <t>海康的同事没有驻场。垂直电镀vcp1自动化问题：小车出现平台失联、直接撞库（使用第一个货架），会突然间不动的现象</t>
+    <t>VCP1自动化问题（海康同事未驻场）：AGV小车出现平台失联、使用第一个货架时直接撞库，以及运行中突然停止不动等现象。</t>
   </si>
   <si>
     <t>1、vcp1线自动化联调，叫料完成（40％）</t>
   </si>
   <si>
-    <t>海康的同事没有驻场。 垂直电镀vcp1自动化问题：1、AGV老是撞货架（使用第一个货架） 2、agv路线不对（应该去放板机，结果跑去收板机） 3、存在识别不到载具的情况</t>
+    <t>VCP1自动化问题（海康同事未驻场）：① AGV频繁撞上第一个货架；② AGV路线错误，应去放板机却前往收板机；③ 存在无法识别载具的情况。</t>
   </si>
   <si>
     <r>
@@ -1310,13 +1310,437 @@
     </r>
   </si>
   <si>
-    <t>海康的同事没有驻场。垂直电镀vcp1自动化问题：AGV倒车入第一个货架的位置不对，无法入库，改为使用第二个货架正常运行，第一个货架撞库问题尚未解决</t>
+    <t>VCP1自动化问题（海康同事未驻场）：AGV倒车进入第一个货架时定位不准，无法入库；改用第二个货架后可正常运行，第一个货架撞库问题尚未解决。</t>
   </si>
   <si>
     <t>1、vcp1线自动化联调（75％）</t>
   </si>
   <si>
-    <t>海康的同事下午才开始驻场。垂直电镀vcp1自动化问题：1、小车进入放板机与设备的升降零件发生剐蹭（光栅铁片扭曲），导致AGV小车掉漆，证实是光栅铁片高度问题 2、退空载时，倒车入点位的位置不对（底码位置有误），无法进入放板机2号工位。3、退空载回去的路线也不对，海康库位编码需要更新，导致小车退空载路线不正确</t>
+    <t>VCP1自动化问题（海康同事下午才到场）：① 小车进入放板机时与设备升降零件发生剐蹭，导致光栅铁片扭曲、AGV掉漆，已确认为光栅铁片高度问题；② 退空载时倒车入点位位置错误（底码位置有误），无法进入放板机2号工位；③ 退空载返回路线错误，需更新海康库位编码，导致小车退空载路径不正确。</t>
+  </si>
+  <si>
+    <r>
+      <t>1、垂直电镀VCP2自动化测试（40%）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2、VCP1线PDA配方下发问题排查（100%）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3、VCP2线PDA配方下发问题排查（70%）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4、PLB线PDA配方下发问题排查（50%）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>VCP1：早上设备在生产暂停自动化测试。主线设备未接收PDA配方下发指令，需联系RMS及设备厂商排查。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>VCP2：① 早上进行自动化测试时发现：RMS未维护VCP2主线配方（invoke接口数据缺失）；② PDA配方下发时设备回复S6F11超时，需联系设备厂商核对，下午设备在生产暂停自动化测试。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>VCP线整体：下午4点半因甲方经理前来验收，暂停所有测试。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PLB： 现场无正式工单，使用测试工单测试，但主线设备未维护对应的料号与Lot，导致无法下发。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1、垂直电镀VCP2自动化测试（70%）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2、VCP2线PDA配方下发问题排查（90%）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1、agv小车经常与平台失联</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2、vcp2线设备没有自动切换在线模式（待找厂商确认）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3、VCP2线PDA配方下发失败，pda接口，rms返回数据缺少配方id（有待验证）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4、VCP2工作流放板机工位一的载具编码未写入点位（待验证）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5、plb、vcp1没有工单无法测pda下发（vcp1设备在维护）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1、垂直电镀VCP2自动化测试（80%）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2、PLB线PDA配方下发问题排查（设备没有维护对应lto、料号导致）（100%）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3、VCP2线PDA配方下发问题排查（设备没有维护对应料号导致）（100%）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>投收板机：VCP1，配方下发后设备没有请求放板，收板机二号工位载具编码为空（下周一找设备排查）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>自动化物流（海康）：小车与平台经常失联严重（一整天高频率间歇性/长期性失联）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>软件集成（SIE）：VCP1自动化叫料接口报错mes获取任务lot与载具绑定不正确（延误时间2小时，已解决）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>生产/工艺：三条线都是因为设备没有维护对应lot、料号导致pda下发不到设备（原因是生产没有配置正确lot和料号，以及使用工单错误——使用转场工单）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>维护：plb在保养维护，无法自动化测试</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>待办项：VCP2线小车调用Eap的工作流TackComplete接口后，收板机1号工位载具编码没有写入值（正在排查）</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1329,7 +1753,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1344,6 +1768,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -1831,137 +2261,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1976,24 +2406,43 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
           <etc:displayText val="2"/>
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
       <extLst>
         <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
           <etc:displayText val="2"/>
         </ext>
       </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+      <extLst>
+        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
+          <etc:displayText val="2"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+      <extLst>
+        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
+          <etc:displayText val="2"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2306,13 +2755,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="22.1111111111111" customWidth="1"/>
     <col min="2" max="2" width="102.407407407407" customWidth="1"/>
     <col min="3" max="3" width="20.6759259259259" customWidth="1"/>
-    <col min="4" max="4" width="24.4444444444444" customWidth="1"/>
+    <col min="4" max="4" width="108.87962962963" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2325,7 +2774,7 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
@@ -2333,452 +2782,485 @@
       </c>
     </row>
     <row r="2" ht="88" customHeight="1" spans="1:5">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>46085</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="6"/>
     </row>
     <row r="3" ht="119" customHeight="1" spans="1:5">
-      <c r="A3" s="3">
+      <c r="A3" s="4">
         <v>46086</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="6"/>
     </row>
     <row r="4" ht="88" customHeight="1" spans="1:5">
-      <c r="A4" s="3">
+      <c r="A4" s="4">
         <v>46087</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="6"/>
     </row>
     <row r="5" ht="88" customHeight="1" spans="1:5">
-      <c r="A5" s="3">
+      <c r="A5" s="4">
         <v>46088</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="5"/>
+      <c r="D5" s="6"/>
     </row>
     <row r="6" ht="88" customHeight="1" spans="1:5">
-      <c r="A6" s="3">
+      <c r="A6" s="4">
         <v>46090</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="5"/>
+      <c r="D6" s="6"/>
     </row>
     <row r="7" ht="88" customHeight="1" spans="1:5">
-      <c r="A7" s="3">
+      <c r="A7" s="4">
         <v>46091</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="5"/>
+      <c r="D7" s="6"/>
     </row>
     <row r="8" ht="88" customHeight="1" spans="1:5">
-      <c r="A8" s="3">
+      <c r="A8" s="4">
         <v>46092</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="5"/>
+      <c r="D8" s="6"/>
     </row>
     <row r="9" ht="88" customHeight="1" spans="1:5">
-      <c r="A9" s="3">
+      <c r="A9" s="4">
         <v>46093</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="5"/>
+      <c r="D9" s="6"/>
     </row>
     <row r="10" ht="115" customHeight="1" spans="1:5">
-      <c r="A10" s="3">
+      <c r="A10" s="4">
         <v>46094</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="5"/>
+      <c r="D10" s="6"/>
     </row>
     <row r="11" ht="115" customHeight="1" spans="1:5">
-      <c r="A11" s="3">
+      <c r="A11" s="4">
         <v>46097</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="5"/>
+      <c r="D11" s="6"/>
     </row>
     <row r="12" ht="115" customHeight="1" spans="1:5">
-      <c r="A12" s="3">
+      <c r="A12" s="4">
         <v>46098</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="5"/>
+      <c r="D12" s="6"/>
     </row>
     <row r="13" ht="88" customHeight="1" spans="1:5">
-      <c r="A13" s="3">
+      <c r="A13" s="4">
         <v>46099</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="5"/>
+      <c r="D13" s="6"/>
     </row>
     <row r="14" ht="88" customHeight="1" spans="1:5">
-      <c r="A14" s="3">
+      <c r="A14" s="4">
         <v>46100</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="5"/>
+      <c r="D14" s="6"/>
     </row>
     <row r="15" ht="88" customHeight="1" spans="1:5">
-      <c r="A15" s="3">
+      <c r="A15" s="4">
         <v>46101</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="5"/>
+      <c r="D15" s="6"/>
     </row>
     <row r="16" ht="88" customHeight="1" spans="1:5">
-      <c r="A16" s="3">
+      <c r="A16" s="4">
         <v>46105</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="5"/>
+      <c r="D16" s="6"/>
     </row>
     <row r="17" ht="88" customHeight="1" spans="1:4">
-      <c r="A17" s="3">
+      <c r="A17" s="4">
         <v>46106</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="5"/>
+      <c r="D17" s="6"/>
     </row>
     <row r="18" ht="88" customHeight="1" spans="1:4">
-      <c r="A18" s="3">
+      <c r="A18" s="4">
         <v>46107</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="5"/>
+      <c r="D18" s="6"/>
     </row>
     <row r="19" ht="88" customHeight="1" spans="1:4">
-      <c r="A19" s="3">
+      <c r="A19" s="4">
         <v>46108</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="5"/>
+      <c r="D19" s="6"/>
     </row>
     <row r="20" ht="88" customHeight="1" spans="1:4">
-      <c r="A20" s="3">
+      <c r="A20" s="4">
         <v>46109</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="5"/>
+      <c r="D20" s="6"/>
     </row>
     <row r="21" ht="88" customHeight="1" spans="1:4">
-      <c r="A21" s="3">
+      <c r="A21" s="4">
         <v>46111</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="5"/>
+      <c r="D21" s="6"/>
     </row>
     <row r="22" ht="88" customHeight="1" spans="1:4">
-      <c r="A22" s="3">
+      <c r="A22" s="4">
         <v>46112</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="5"/>
+      <c r="D22" s="6"/>
     </row>
     <row r="23" ht="88" customHeight="1" spans="1:4">
-      <c r="A23" s="3">
+      <c r="A23" s="4">
         <v>46113</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="5"/>
+      <c r="D23" s="6"/>
     </row>
     <row r="24" ht="88" customHeight="1" spans="1:4">
-      <c r="A24" s="3">
+      <c r="A24" s="4">
         <v>46114</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D24" s="5"/>
+      <c r="D24" s="6"/>
     </row>
     <row r="25" ht="88" customHeight="1" spans="1:4">
-      <c r="A25" s="3">
+      <c r="A25" s="4">
         <v>46115</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D25" s="5"/>
+      <c r="D25" s="6"/>
     </row>
     <row r="26" ht="88" customHeight="1" spans="1:4">
-      <c r="A26" s="3">
+      <c r="A26" s="4">
         <v>46119</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="5"/>
+      <c r="D26" s="6"/>
     </row>
     <row r="27" ht="88" customHeight="1" spans="1:4">
-      <c r="A27" s="3">
+      <c r="A27" s="4">
         <v>46120</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="5"/>
+      <c r="D27" s="6"/>
     </row>
     <row r="28" customFormat="1" ht="88" customHeight="1" spans="1:4">
-      <c r="A28" s="3">
+      <c r="A28" s="4">
         <v>46121</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="5"/>
+      <c r="D28" s="6"/>
     </row>
     <row r="29" customFormat="1" ht="88" customHeight="1" spans="1:4">
-      <c r="A29" s="3">
+      <c r="A29" s="4">
         <v>46122</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D29" s="5"/>
+      <c r="D29" s="6"/>
     </row>
     <row r="30" ht="88" customHeight="1" spans="1:4">
-      <c r="A30" s="3">
+      <c r="A30" s="4">
         <v>46125</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D30" s="5"/>
+      <c r="D30" s="6"/>
     </row>
     <row r="31" ht="88" customHeight="1" spans="1:4">
-      <c r="A31" s="3">
+      <c r="A31" s="4">
         <v>46126</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="5"/>
+      <c r="D31" s="6"/>
     </row>
     <row r="32" ht="88" customHeight="1" spans="1:4">
-      <c r="A32" s="3">
+      <c r="A32" s="4">
         <v>46127</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="5"/>
+      <c r="D32" s="6"/>
     </row>
     <row r="33" ht="88" customHeight="1" spans="1:4">
-      <c r="A33" s="3">
+      <c r="A33" s="4">
         <v>46128</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D33" s="5"/>
+      <c r="D33" s="6"/>
     </row>
     <row r="34" ht="88" customHeight="1" spans="1:4">
-      <c r="A34" s="3">
+      <c r="A34" s="4">
         <v>46129</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D34" s="5"/>
+      <c r="D34" s="6"/>
     </row>
     <row r="35" ht="88" customHeight="1" spans="1:4">
-      <c r="A35" s="3">
+      <c r="A35" s="4">
         <v>46132</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D35" s="5"/>
+      <c r="D35" s="6"/>
     </row>
     <row r="36" ht="88" customHeight="1" spans="1:4">
-      <c r="A36" s="3">
+      <c r="A36" s="4">
         <v>46133</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D36" s="5"/>
+      <c r="D36" s="6"/>
     </row>
     <row r="37" ht="88" customHeight="1" spans="1:4">
-      <c r="A37" s="3">
+      <c r="A37" s="4">
         <v>46134</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D37" s="5"/>
+      <c r="D37" s="6"/>
     </row>
     <row r="38" ht="43.2" spans="1:4">
-      <c r="A38" s="3">
+      <c r="A38" s="4">
         <v>46135</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D38" s="5"/>
+      <c r="D38" s="6"/>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="3">
+      <c r="A39" s="4">
         <v>46136</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D39" s="5"/>
+      <c r="D39" s="6"/>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="3">
+      <c r="A40" s="4">
         <v>46137</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D40" s="5"/>
+      <c r="D40" s="6"/>
     </row>
     <row r="41" ht="43.2" spans="1:4">
-      <c r="A41" s="3">
+      <c r="A41" s="4">
         <v>46139</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="5"/>
+      <c r="D41" s="6"/>
     </row>
     <row r="42" ht="43.2" spans="1:4">
-      <c r="A42" s="3">
+      <c r="A42" s="4">
         <v>46140</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D42" s="5"/>
+      <c r="D42" s="6"/>
     </row>
     <row r="43" ht="43.2" spans="1:4">
-      <c r="A43" s="3">
+      <c r="A43" s="4">
         <v>46141</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D43" s="5"/>
+      <c r="D43" s="6"/>
     </row>
     <row r="44" ht="28.8" spans="1:4">
-      <c r="A44" s="3">
+      <c r="A44" s="4">
         <v>46142</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D44" s="5"/>
+      <c r="D44" s="6"/>
     </row>
     <row r="45" ht="28.8" spans="1:4">
-      <c r="A45" s="3">
+      <c r="A45" s="4">
         <v>46148</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D45" s="5"/>
+      <c r="D45" s="6"/>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="3">
+      <c r="A46" s="4">
         <v>46149</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D46" s="5"/>
+      <c r="D46" s="6"/>
     </row>
     <row r="47" ht="28.8" spans="1:4">
-      <c r="A47" s="3">
+      <c r="A47" s="4">
         <v>46150</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D47" s="7" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="3">
+      <c r="A48" s="4">
         <v>46151</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="D48" s="7" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="49" ht="28.8" spans="1:4">
-      <c r="A49" s="3">
+      <c r="A49" s="4">
         <v>46153</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="D49" s="7" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="3">
+      <c r="A50" s="4">
         <v>46154</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="D50" s="7" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="51" ht="87" customHeight="1" spans="1:4">
+      <c r="A51" s="4">
+        <v>46155</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="52" ht="72" spans="1:4">
+      <c r="A52" s="4">
+        <v>46156</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" ht="158.4" spans="1:4">
+      <c r="A53" s="4">
+        <v>46157</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
